--- a/site/examples/sample-template.xlsx
+++ b/site/examples/sample-template.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
-    <sheet sheetId="2" name="Report" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Renewal Report" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>Sample operator report</t>
+    <t>Sample customer renewal report</t>
   </si>
   <si>
     <t>source_sheet</t>
@@ -35,40 +35,55 @@
     <t>output_file_pattern</t>
   </si>
   <si>
-    <t>sample-result.xlsx</t>
-  </si>
-  <si>
-    <t>Monthly Customer Report</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Amount</t>
+    <t>customer-renewal-report.xlsx</t>
+  </si>
+  <si>
+    <t>Customer Renewal Pipeline</t>
+  </si>
+  <si>
+    <t>Operators upload raw.xlsx and this template. Rules are archived in _config.</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>{{ COUNT() }}</t>
+  </si>
+  <si>
+    <t>Priority rule</t>
+  </si>
+  <si>
+    <t>Renewal &gt; 10,000</t>
+  </si>
+  <si>
+    <t>Account</t>
   </si>
   <si>
     <t>Region</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>{{ [Customer] }}</t>
-  </si>
-  <si>
-    <t>{{ [Amount] }}</t>
+    <t>Renewal</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Tier</t>
+  </si>
+  <si>
+    <t>{{ [Account] }}</t>
   </si>
   <si>
     <t>{{ [Region] }}</t>
   </si>
   <si>
-    <t>{{ [Status] }}</t>
-  </si>
-  <si>
-    <t>Template note</t>
-  </si>
-  <si>
-    <t>Rules live in _config. Operators only upload raw Excel and download this finished workbook.</t>
+    <t>{{ [Renewal] }}</t>
+  </si>
+  <si>
+    <t>{{ [Owner] }}</t>
+  </si>
+  <si>
+    <t>{{ IF([Renewal] &gt; 10000, Priority, Standard) }}</t>
   </si>
 </sst>
 </file>
@@ -86,22 +101,22 @@
     <font>
       <b/>
       <color rgb="FF185C37"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <i/>
+      <color rgb="FF68716D"/>
     </font>
     <font>
       <b/>
       <color rgb="FF185C37"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF68716D"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,11 +125,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE7F3EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF217846"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -126,8 +146,17 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFD9E2DC"/>
+        <color rgb="FFC8D0CA"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFC8D0CA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD9E2DC"/>
       </bottom>
@@ -137,18 +166,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,6 +524,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -531,65 +569,85 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/site/examples/sample-template.xlsx
+++ b/site/examples/sample-template.xlsx
@@ -26,10 +26,10 @@
     <t>Raw</t>
   </si>
   <si>
-    <t>source_header_range</t>
-  </si>
-  <si>
-    <t>A1:D1</t>
+    <t>source_table</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>output_file_pattern</t>
@@ -83,7 +83,7 @@
     <t>{{ [Owner] }}</t>
   </si>
   <si>
-    <t>{{ IF([Renewal] &gt; 10000, Priority, Standard) }}</t>
+    <t>{{ IF([Renewal] &gt; 10000, "Priority", "Standard") }}</t>
   </si>
 </sst>
 </file>
